--- a/docs/primer_design/primer_order_6amp_pool32.xlsx
+++ b/docs/primer_design/primer_order_6amp_pool32.xlsx
@@ -505,7 +505,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>脱靶：人 hg19 和猪 susScr3（Sscrofa10.2）全基因组，≤2 错配、3′端 8 nt 完全匹配；人基因组 A5-R 两条合计 10 个位点（单条未拆分，猪基因组分别 9 和 8）。</t>
+          <t>脱靶（最终池 32 条、196 个展开，均已扫描）：人 hg19 ≤2 错配位点 546 个（2.8/展开），线粒体 ≤3 错配 1 个；猪 susScr3（Sscrofa10.2）≤2 错配位点 915 个（4.7/展开，其中 A1-F.SNAP 占 492），线粒体 0 个。正反向引物配成的潜在产物（≤2000 bp）：≤2 错配 0 个；≤3 错配 人 6 个（292–1875 bp）、猪 15 个（212–1923 bp）。短于 500 bp 的各 1 个：人 chr5 292 bp（A1-R.8s 自身两端）、猪 chr1 212 bp（A1-R.8s × A5-F.3）。</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2109,7 +2109,9 @@
           <t>54.2–61.5</t>
         </is>
       </c>
-      <c r="J27" s="6" t="n"/>
+      <c r="J27" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="K27" s="6" t="n">
         <v>9</v>
       </c>
@@ -2128,7 +2130,7 @@
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>起点 1188；人基因组两条合计 10 个位点</t>
+          <t>起点 1188（人基因组此前旧 A5-R 为 1281 个位点）</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2174,9 @@
           <t>55.4–63.4</t>
         </is>
       </c>
-      <c r="J28" s="6" t="n"/>
+      <c r="J28" s="6" t="n">
+        <v>5</v>
+      </c>
       <c r="K28" s="6" t="n">
         <v>8</v>
       </c>
@@ -2191,7 +2195,7 @@
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>起点 1188（人基因组此前旧 A5-R 为 1281 个位点）</t>
         </is>
       </c>
     </row>
@@ -2630,6 +2634,7 @@
       </c>
       <c r="O35" s="6" t="inlineStr"/>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -2645,6 +2650,8 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
